--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\RQSD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2704A86-BF7B-4C73-BDF4-A433010F241F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B661A6-F510-434A-B3E0-7371A419171D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9120" yWindow="690" windowWidth="19110" windowHeight="16425" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="CQSD" sheetId="2" r:id="rId2"/>
-    <sheet name="RQSD" sheetId="3" r:id="rId3"/>
+    <sheet name="RQSD-CQSD" sheetId="2" r:id="rId2"/>
+    <sheet name="RQSD-RQSD" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -195,7 +195,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -205,7 +205,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -512,22 +511,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="84.54296875" customWidth="1"/>
+    <col min="2" max="2" width="84.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -535,35 +534,35 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
     </row>
   </sheetData>
@@ -578,13 +577,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.453125" customWidth="1"/>
-    <col min="2" max="2" width="28.453125" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
@@ -679,7 +678,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -774,7 +773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -869,7 +868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -964,7 +963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -1059,7 +1058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -1154,7 +1153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1249,7 +1248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1344,7 +1343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1439,7 +1438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1534,7 +1533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1629,7 +1628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1724,7 +1723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1819,7 +1818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1944,7 +1943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -2039,7 +2038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -2134,7 +2133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -2229,7 +2228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -2324,7 +2323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -2419,7 +2418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -2514,7 +2513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -2609,7 +2608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -2704,7 +2703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -2799,7 +2798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>28</v>
       </c>
@@ -2894,7 +2893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>29</v>
       </c>
@@ -3000,13 +2999,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.453125" customWidth="1"/>
-    <col min="2" max="2" width="28.453125" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
@@ -3101,7 +3100,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -3196,7 +3195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -3291,7 +3290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -3386,7 +3385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -3481,7 +3480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -3576,7 +3575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3671,7 +3670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -3766,7 +3765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -3861,7 +3860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -3956,7 +3955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -4051,7 +4050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -4146,7 +4145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -4241,7 +4240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -4366,7 +4365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -4461,7 +4460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -4556,7 +4555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -4651,7 +4650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -4746,7 +4745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -4841,7 +4840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -4936,7 +4935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -5031,7 +5030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -5126,7 +5125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -5221,7 +5220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>28</v>
       </c>
@@ -5316,7 +5315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>29</v>
       </c>
